--- a/Plantilla migración equipos.xlsx
+++ b/Plantilla migración equipos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvelascot\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvelascot\Documents\Proyectos Tecnología\inventorySistem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{233B414C-E8A1-43E7-9470-648AA44C9877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4820AC6D-F0C3-4FAE-AE6E-62B7E6F5D7A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BFD753E0-84D2-48D5-8050-D9D9E9B34C4B}"/>
   </bookViews>
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="412">
   <si>
     <t>usuario</t>
   </si>
@@ -1305,6 +1305,18 @@
   </si>
   <si>
     <t>nombre</t>
+  </si>
+  <si>
+    <t>centro_costo</t>
+  </si>
+  <si>
+    <t>6SZYS34344</t>
+  </si>
+  <si>
+    <t>8V0ZS34TRESA</t>
+  </si>
+  <si>
+    <t>SSD256GB</t>
   </si>
 </sst>
 </file>
@@ -1364,7 +1376,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1401,8 +1413,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -1558,11 +1576,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
@@ -1631,9 +1660,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1680,11 +1706,16 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="10">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1710,21 +1741,17 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
         </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
+        <right/>
         <top style="thin">
           <color rgb="FF000000"/>
         </top>
         <bottom style="thin">
           <color rgb="FF000000"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -2024,20 +2051,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{50A4A928-1E49-4C5A-AF37-F776A10C9A95}" name="Tabla2" displayName="Tabla2" ref="A1:K110" totalsRowShown="0" headerRowDxfId="8">
-  <autoFilter ref="A1:K110" xr:uid="{50A4A928-1E49-4C5A-AF37-F776A10C9A95}"/>
-  <tableColumns count="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{50A4A928-1E49-4C5A-AF37-F776A10C9A95}" name="Tabla2" displayName="Tabla2" ref="A1:L110" totalsRowShown="0" headerRowDxfId="9">
+  <autoFilter ref="A1:L110" xr:uid="{50A4A928-1E49-4C5A-AF37-F776A10C9A95}"/>
+  <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{94EEDDB5-440C-4202-B416-852FB1BA9688}" name="nombre"/>
-    <tableColumn id="2" xr3:uid="{D8FF830E-3917-4A6F-A2DF-4FD462FC1E63}" name="usuario" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{D05D9340-1204-4610-BAC3-24BFE9CA8CD1}" name="marca" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{C4EFA469-6DDB-427D-A2B7-EE2522A92F79}" name="modelo" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{82743EFC-A75A-4954-87A6-B497A3B812C8}" name="tipo" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{D8FF830E-3917-4A6F-A2DF-4FD462FC1E63}" name="usuario" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{D05D9340-1204-4610-BAC3-24BFE9CA8CD1}" name="marca" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{C4EFA469-6DDB-427D-A2B7-EE2522A92F79}" name="modelo" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{82743EFC-A75A-4954-87A6-B497A3B812C8}" name="tipo" dataDxfId="5"/>
     <tableColumn id="6" xr3:uid="{31EBD4B8-8BA8-43DC-B7C9-B6361B9D5EB7}" name="procesador"/>
-    <tableColumn id="7" xr3:uid="{63DA8486-8832-4DDA-98B7-C4FAA96209F5}" name="ram" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{35A9F25F-FBE9-4F10-8029-A3988BCBBEFA}" name="disco_duro" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{63DA8486-8832-4DDA-98B7-C4FAA96209F5}" name="ram" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{35A9F25F-FBE9-4F10-8029-A3988BCBBEFA}" name="disco_duro" dataDxfId="3"/>
     <tableColumn id="9" xr3:uid="{7E09CEBB-5975-41D3-964A-9D1951834654}" name="serial"/>
-    <tableColumn id="10" xr3:uid="{622BEFBC-0F19-4525-A800-2CDBD6FEDAB0}" name="contrato" dataDxfId="1"/>
-    <tableColumn id="11" xr3:uid="{1AE382CD-3DE2-42B9-9D6E-05420CE83D69}" name="costo_unitario" dataDxfId="0"/>
+    <tableColumn id="10" xr3:uid="{622BEFBC-0F19-4525-A800-2CDBD6FEDAB0}" name="contrato" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{1AE382CD-3DE2-42B9-9D6E-05420CE83D69}" name="costo_unitario" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{FEECCB62-821F-4A66-BC15-C847355E1788}" name="centro_costo" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2377,7 +2405,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B76F66E7-7E63-45B2-9F49-C14228A5EEA4}">
-  <dimension ref="A1:K128"/>
+  <dimension ref="A1:L128"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="13" customWidth="1"/>
@@ -2385,42 +2413,45 @@
     <col min="11" max="11" width="19.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="40" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
+    <row r="1" spans="1:12" s="39" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="37" t="s">
         <v>407</v>
       </c>
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="38" t="s">
+      <c r="C1" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="38" t="s">
+      <c r="E1" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="38" t="s">
+      <c r="F1" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="38" t="s">
+      <c r="G1" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="38" t="s">
+      <c r="H1" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="38" t="s">
+      <c r="I1" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="38" t="s">
+      <c r="J1" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="39" t="s">
+      <c r="K1" s="38" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L1" s="37" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -2449,13 +2480,16 @@
         <v>18</v>
       </c>
       <c r="J2" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L2" s="41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
@@ -2484,13 +2518,16 @@
         <v>22</v>
       </c>
       <c r="J3" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K3" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L3" s="41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>23</v>
       </c>
@@ -2519,13 +2556,16 @@
         <v>27</v>
       </c>
       <c r="J4" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K4" s="4">
         <v>183000</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L4" s="41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>28</v>
       </c>
@@ -2554,13 +2594,16 @@
         <v>30</v>
       </c>
       <c r="J5" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K5" s="4">
         <v>183000</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L5" s="41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>31</v>
       </c>
@@ -2589,13 +2632,16 @@
         <v>33</v>
       </c>
       <c r="J6" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K6" s="4">
         <v>183000</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L6" s="41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>34</v>
       </c>
@@ -2624,13 +2670,16 @@
         <v>36</v>
       </c>
       <c r="J7" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K7" s="4">
         <v>183000</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L7" s="41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>37</v>
       </c>
@@ -2659,13 +2708,16 @@
         <v>39</v>
       </c>
       <c r="J8" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K8" s="4">
         <v>183000</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L8" s="41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>40</v>
       </c>
@@ -2694,13 +2746,16 @@
         <v>42</v>
       </c>
       <c r="J9" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K9" s="4">
         <v>183000</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L9" s="41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>43</v>
       </c>
@@ -2729,13 +2784,16 @@
         <v>46</v>
       </c>
       <c r="J10" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K10" s="4">
         <v>151558</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L10" s="41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>47</v>
       </c>
@@ -2764,13 +2822,16 @@
         <v>49</v>
       </c>
       <c r="J11" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K11" s="4">
         <v>151558</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L11" s="41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>50</v>
       </c>
@@ -2799,13 +2860,16 @@
         <v>52</v>
       </c>
       <c r="J12" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K12" s="4">
         <v>92000</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L12" s="41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>53</v>
       </c>
@@ -2834,13 +2898,16 @@
         <v>56</v>
       </c>
       <c r="J13" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K13" s="7">
         <v>136000</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L13" s="41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>57</v>
       </c>
@@ -2869,13 +2936,16 @@
         <v>59</v>
       </c>
       <c r="J14" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K14" s="8">
         <v>116055</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L14" s="41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
         <v>60</v>
       </c>
@@ -2904,13 +2974,16 @@
         <v>62</v>
       </c>
       <c r="J15" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K15" s="7">
         <v>183506</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L15" s="41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>63</v>
       </c>
@@ -2939,13 +3012,16 @@
         <v>65</v>
       </c>
       <c r="J16" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K16" s="4">
         <v>151558</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L16" s="41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>66</v>
       </c>
@@ -2974,13 +3050,16 @@
         <v>68</v>
       </c>
       <c r="J17" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K17" s="8">
         <v>116055</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L17" s="41">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>69</v>
       </c>
@@ -3009,13 +3088,16 @@
         <v>71</v>
       </c>
       <c r="J18" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K18" s="4">
         <v>92000</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L18" s="41">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>72</v>
       </c>
@@ -3044,13 +3126,16 @@
         <v>74</v>
       </c>
       <c r="J19" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K19" s="4">
         <v>151558</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L19" s="41">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>75</v>
       </c>
@@ -3079,13 +3164,16 @@
         <v>77</v>
       </c>
       <c r="J20" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K20" s="8">
         <v>116055</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L20" s="41">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>78</v>
       </c>
@@ -3114,13 +3202,16 @@
         <v>80</v>
       </c>
       <c r="J21" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K21" s="4">
         <v>151558</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L21" s="41">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>81</v>
       </c>
@@ -3149,13 +3240,16 @@
         <v>83</v>
       </c>
       <c r="J22" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K22" s="4">
         <v>151558</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L22" s="41">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>84</v>
       </c>
@@ -3184,13 +3278,16 @@
         <v>86</v>
       </c>
       <c r="J23" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K23" s="4">
         <v>151558</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L23" s="41">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
         <v>87</v>
       </c>
@@ -3219,13 +3316,16 @@
         <v>89</v>
       </c>
       <c r="J24" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K24" s="4">
         <v>92000</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L24" s="41">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>90</v>
       </c>
@@ -3254,13 +3354,16 @@
         <v>92</v>
       </c>
       <c r="J25" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K25" s="8">
         <v>116055</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L25" s="41">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>93</v>
       </c>
@@ -3289,13 +3392,16 @@
         <v>97</v>
       </c>
       <c r="J26" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K26" s="12">
         <v>152640</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L26" s="41">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>98</v>
       </c>
@@ -3324,13 +3430,16 @@
         <v>100</v>
       </c>
       <c r="J27" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K27" s="8">
         <v>116055</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L27" s="41">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A28" s="13" t="s">
         <v>101</v>
       </c>
@@ -3359,13 +3468,16 @@
         <v>104</v>
       </c>
       <c r="J28" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K28" s="16" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L28" s="41">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>105</v>
       </c>
@@ -3394,13 +3506,16 @@
         <v>107</v>
       </c>
       <c r="J29" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K29" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L29" s="41">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A30" s="18" t="s">
         <v>108</v>
       </c>
@@ -3429,13 +3544,16 @@
         <v>109</v>
       </c>
       <c r="J30" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K30" s="21" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L30" s="41">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A31" s="18" t="s">
         <v>110</v>
       </c>
@@ -3464,13 +3582,16 @@
         <v>113</v>
       </c>
       <c r="J31" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K31" s="21" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L31" s="41">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>114</v>
       </c>
@@ -3499,13 +3620,16 @@
         <v>116</v>
       </c>
       <c r="J32" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K32" s="8">
         <v>116055</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L32" s="41">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>117</v>
       </c>
@@ -3534,13 +3658,16 @@
         <v>119</v>
       </c>
       <c r="J33" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K33" s="8">
         <v>116055</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L33" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>120</v>
       </c>
@@ -3569,13 +3696,16 @@
         <v>122</v>
       </c>
       <c r="J34" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K34" s="8">
         <v>116055</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L34" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A35" s="9" t="s">
         <v>123</v>
       </c>
@@ -3604,13 +3734,16 @@
         <v>125</v>
       </c>
       <c r="J35" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K35" s="12">
         <v>152640</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L35" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>126</v>
       </c>
@@ -3639,13 +3772,16 @@
         <v>128</v>
       </c>
       <c r="J36" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K36" s="8">
         <v>116055</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L36" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>129</v>
       </c>
@@ -3674,13 +3810,16 @@
         <v>131</v>
       </c>
       <c r="J37" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K37" s="8">
         <v>116055</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L37" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>132</v>
       </c>
@@ -3709,13 +3848,16 @@
         <v>134</v>
       </c>
       <c r="J38" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K38" s="8">
         <v>116055</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L38" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>135</v>
       </c>
@@ -3744,13 +3886,16 @@
         <v>137</v>
       </c>
       <c r="J39" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K39" s="4">
         <v>151558</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L39" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>138</v>
       </c>
@@ -3779,13 +3924,16 @@
         <v>140</v>
       </c>
       <c r="J40" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K40" s="8">
         <v>116055</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L40" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>141</v>
       </c>
@@ -3814,13 +3962,16 @@
         <v>143</v>
       </c>
       <c r="J41" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K41" s="8">
         <v>116055</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L41" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>144</v>
       </c>
@@ -3849,13 +4000,16 @@
         <v>146</v>
       </c>
       <c r="J42" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K42" s="8">
         <v>116055</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L42" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>147</v>
       </c>
@@ -3884,13 +4038,16 @@
         <v>149</v>
       </c>
       <c r="J43" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K43" s="8">
         <v>116055</v>
       </c>
-    </row>
-    <row r="44" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L43" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>150</v>
       </c>
@@ -3919,13 +4076,16 @@
         <v>152</v>
       </c>
       <c r="J44" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K44" s="4">
         <v>151558</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L44" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>153</v>
       </c>
@@ -3954,13 +4114,16 @@
         <v>155</v>
       </c>
       <c r="J45" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K45" s="8">
         <v>116055</v>
       </c>
-    </row>
-    <row r="46" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L45" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>156</v>
       </c>
@@ -3989,13 +4152,16 @@
         <v>159</v>
       </c>
       <c r="J46" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K46" s="4">
         <v>92000</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L46" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>160</v>
       </c>
@@ -4024,13 +4190,16 @@
         <v>162</v>
       </c>
       <c r="J47" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K47" s="8">
         <v>116055</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L47" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A48" s="17" t="s">
         <v>163</v>
       </c>
@@ -4055,15 +4224,20 @@
       <c r="H48" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="I48" s="24"/>
+      <c r="I48" s="23" t="s">
+        <v>411</v>
+      </c>
       <c r="J48" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K48" s="4">
         <v>92000</v>
       </c>
-    </row>
-    <row r="49" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L48" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>165</v>
       </c>
@@ -4092,13 +4266,16 @@
         <v>167</v>
       </c>
       <c r="J49" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K49" s="4">
         <v>151558</v>
       </c>
-    </row>
-    <row r="50" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L49" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>168</v>
       </c>
@@ -4127,13 +4304,16 @@
         <v>170</v>
       </c>
       <c r="J50" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K50" s="8">
         <v>116055</v>
       </c>
-    </row>
-    <row r="51" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L50" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>171</v>
       </c>
@@ -4162,13 +4342,16 @@
         <v>173</v>
       </c>
       <c r="J51" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K51" s="8">
         <v>116055</v>
       </c>
-    </row>
-    <row r="52" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L51" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>174</v>
       </c>
@@ -4197,13 +4380,16 @@
         <v>176</v>
       </c>
       <c r="J52" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K52" s="8">
         <v>116055</v>
       </c>
-    </row>
-    <row r="53" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L52" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>177</v>
       </c>
@@ -4232,13 +4418,16 @@
         <v>179</v>
       </c>
       <c r="J53" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K53" s="4">
         <v>151558</v>
       </c>
-    </row>
-    <row r="54" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L53" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>180</v>
       </c>
@@ -4267,13 +4456,16 @@
         <v>182</v>
       </c>
       <c r="J54" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K54" s="4">
         <v>151558</v>
       </c>
-    </row>
-    <row r="55" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L54" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A55" s="13" t="s">
         <v>183</v>
       </c>
@@ -4302,13 +4494,16 @@
         <v>185</v>
       </c>
       <c r="J55" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K55" s="16">
         <v>136000</v>
       </c>
-    </row>
-    <row r="56" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L55" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A56" s="18" t="s">
         <v>186</v>
       </c>
@@ -4337,13 +4532,16 @@
         <v>189</v>
       </c>
       <c r="J56" s="3">
-        <v>124587</v>
-      </c>
-      <c r="K56" s="25">
+        <v>1234</v>
+      </c>
+      <c r="K56" s="24">
         <v>152640</v>
       </c>
-    </row>
-    <row r="57" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L56" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>190</v>
       </c>
@@ -4372,13 +4570,16 @@
         <v>192</v>
       </c>
       <c r="J57" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K57" s="4">
         <v>92000</v>
       </c>
-    </row>
-    <row r="58" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L57" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>193</v>
       </c>
@@ -4407,17 +4608,20 @@
         <v>195</v>
       </c>
       <c r="J58" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K58" s="4">
         <v>92000</v>
       </c>
-    </row>
-    <row r="59" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L58" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A59" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="B59" s="26" t="s">
+      <c r="B59" s="25" t="s">
         <v>197</v>
       </c>
       <c r="C59" s="13" t="s">
@@ -4442,13 +4646,16 @@
         <v>198</v>
       </c>
       <c r="J59" s="3">
-        <v>124587</v>
-      </c>
-      <c r="K59" s="27">
+        <v>1234</v>
+      </c>
+      <c r="K59" s="26">
         <v>152640</v>
       </c>
-    </row>
-    <row r="60" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L59" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>199</v>
       </c>
@@ -4477,13 +4684,16 @@
         <v>201</v>
       </c>
       <c r="J60" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K60" s="4">
         <v>136000</v>
       </c>
-    </row>
-    <row r="61" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L60" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A61" s="18" t="s">
         <v>202</v>
       </c>
@@ -4512,13 +4722,16 @@
         <v>204</v>
       </c>
       <c r="J61" s="3">
-        <v>124587</v>
-      </c>
-      <c r="K61" s="25">
+        <v>1234</v>
+      </c>
+      <c r="K61" s="24">
         <v>152640</v>
       </c>
-    </row>
-    <row r="62" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L61" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A62" s="18" t="s">
         <v>205</v>
       </c>
@@ -4547,13 +4760,16 @@
         <v>207</v>
       </c>
       <c r="J62" s="3">
-        <v>124587</v>
-      </c>
-      <c r="K62" s="28" t="s">
+        <v>1234</v>
+      </c>
+      <c r="K62" s="27" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="63" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L62" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A63" s="11" t="s">
         <v>208</v>
       </c>
@@ -4582,13 +4798,16 @@
         <v>210</v>
       </c>
       <c r="J63" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K63" s="4">
         <v>92000</v>
       </c>
-    </row>
-    <row r="64" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L63" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A64" s="11" t="s">
         <v>211</v>
       </c>
@@ -4617,13 +4836,16 @@
         <v>213</v>
       </c>
       <c r="J64" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K64" s="8">
         <v>116055</v>
       </c>
-    </row>
-    <row r="65" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L64" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>214</v>
       </c>
@@ -4652,13 +4874,16 @@
         <v>216</v>
       </c>
       <c r="J65" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K65" s="8">
         <v>116055</v>
       </c>
-    </row>
-    <row r="66" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L65" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>217</v>
       </c>
@@ -4687,13 +4912,16 @@
         <v>219</v>
       </c>
       <c r="J66" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K66" s="8" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="67" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L66" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>220</v>
       </c>
@@ -4722,13 +4950,16 @@
         <v>222</v>
       </c>
       <c r="J67" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K67" s="4">
         <v>151558</v>
       </c>
-    </row>
-    <row r="68" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L67" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>223</v>
       </c>
@@ -4757,13 +4988,16 @@
         <v>224</v>
       </c>
       <c r="J68" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K68" s="4">
         <v>151558</v>
       </c>
-    </row>
-    <row r="69" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L68" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>225</v>
       </c>
@@ -4792,13 +5026,16 @@
         <v>227</v>
       </c>
       <c r="J69" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K69" s="8">
         <v>116055</v>
       </c>
-    </row>
-    <row r="70" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L69" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>228</v>
       </c>
@@ -4827,13 +5064,16 @@
         <v>230</v>
       </c>
       <c r="J70" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K70" s="4">
         <v>151558</v>
       </c>
-    </row>
-    <row r="71" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L70" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>231</v>
       </c>
@@ -4862,13 +5102,16 @@
         <v>233</v>
       </c>
       <c r="J71" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K71" s="4">
         <v>151558</v>
       </c>
-    </row>
-    <row r="72" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L71" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>234</v>
       </c>
@@ -4897,13 +5140,16 @@
         <v>236</v>
       </c>
       <c r="J72" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K72" s="8">
         <v>116055</v>
       </c>
-    </row>
-    <row r="73" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L72" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>237</v>
       </c>
@@ -4932,13 +5178,16 @@
         <v>239</v>
       </c>
       <c r="J73" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K73" s="8">
         <v>116055</v>
       </c>
-    </row>
-    <row r="74" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L73" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>240</v>
       </c>
@@ -4967,13 +5216,16 @@
         <v>242</v>
       </c>
       <c r="J74" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K74" s="4">
         <v>151558</v>
       </c>
-    </row>
-    <row r="75" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L74" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>243</v>
       </c>
@@ -5002,13 +5254,16 @@
         <v>245</v>
       </c>
       <c r="J75" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K75" s="8">
         <v>116055</v>
       </c>
-    </row>
-    <row r="76" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L75" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>246</v>
       </c>
@@ -5037,13 +5292,16 @@
         <v>248</v>
       </c>
       <c r="J76" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K76" s="4">
         <v>92000</v>
       </c>
-    </row>
-    <row r="77" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L76" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>249</v>
       </c>
@@ -5072,13 +5330,16 @@
         <v>251</v>
       </c>
       <c r="J77" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K77" s="4">
         <v>92000</v>
       </c>
-    </row>
-    <row r="78" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L77" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>252</v>
       </c>
@@ -5107,13 +5368,16 @@
         <v>254</v>
       </c>
       <c r="J78" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K78" s="4">
         <v>92000</v>
       </c>
-    </row>
-    <row r="79" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L78" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>255</v>
       </c>
@@ -5142,13 +5406,16 @@
         <v>257</v>
       </c>
       <c r="J79" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K79" s="4">
         <v>92000</v>
       </c>
-    </row>
-    <row r="80" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L79" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>258</v>
       </c>
@@ -5177,13 +5444,16 @@
         <v>260</v>
       </c>
       <c r="J80" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K80" s="4">
         <v>151558</v>
       </c>
-    </row>
-    <row r="81" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L80" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>261</v>
       </c>
@@ -5212,13 +5482,16 @@
         <v>263</v>
       </c>
       <c r="J81" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K81" s="8">
         <v>116055</v>
       </c>
-    </row>
-    <row r="82" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L81" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>264</v>
       </c>
@@ -5247,13 +5520,16 @@
         <v>266</v>
       </c>
       <c r="J82" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K82" s="4">
         <v>92000</v>
       </c>
-    </row>
-    <row r="83" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L82" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>267</v>
       </c>
@@ -5282,13 +5558,16 @@
         <v>269</v>
       </c>
       <c r="J83" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K83" s="8">
         <v>116055</v>
       </c>
-    </row>
-    <row r="84" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L83" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>270</v>
       </c>
@@ -5317,13 +5596,16 @@
         <v>271</v>
       </c>
       <c r="J84" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K84" s="8">
         <v>116055</v>
       </c>
-    </row>
-    <row r="85" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L84" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>272</v>
       </c>
@@ -5352,13 +5634,16 @@
         <v>274</v>
       </c>
       <c r="J85" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K85" s="4">
         <v>151558</v>
       </c>
-    </row>
-    <row r="86" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L85" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>275</v>
       </c>
@@ -5387,83 +5672,92 @@
         <v>277</v>
       </c>
       <c r="J86" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K86" s="8">
         <v>116055</v>
       </c>
-    </row>
-    <row r="87" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A87" s="29" t="s">
+      <c r="L86" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A87" s="28" t="s">
         <v>278</v>
       </c>
-      <c r="B87" s="29" t="s">
+      <c r="B87" s="28" t="s">
         <v>279</v>
       </c>
-      <c r="C87" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="D87" s="29" t="s">
+      <c r="C87" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="D87" s="28" t="s">
         <v>158</v>
       </c>
-      <c r="E87" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="F87" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="G87" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="H87" s="29" t="s">
+      <c r="E87" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="F87" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="G87" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="H87" s="28" t="s">
         <v>280</v>
       </c>
-      <c r="I87" s="29" t="s">
+      <c r="I87" s="28" t="s">
         <v>281</v>
       </c>
       <c r="J87" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K87" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="88" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A88" s="29" t="s">
+      <c r="L87" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A88" s="28" t="s">
         <v>282</v>
       </c>
-      <c r="B88" s="29" t="s">
+      <c r="B88" s="28" t="s">
         <v>283</v>
       </c>
-      <c r="C88" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="D88" s="29" t="s">
+      <c r="C88" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="D88" s="28" t="s">
         <v>158</v>
       </c>
-      <c r="E88" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="F88" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="G88" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="H88" s="29" t="s">
+      <c r="E88" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="F88" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="G88" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="H88" s="28" t="s">
         <v>280</v>
       </c>
-      <c r="I88" s="29" t="s">
+      <c r="I88" s="28" t="s">
         <v>284</v>
       </c>
       <c r="J88" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K88" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="89" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L88" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>285</v>
       </c>
@@ -5492,13 +5786,16 @@
         <v>287</v>
       </c>
       <c r="J89" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K89" s="4">
         <v>151558</v>
       </c>
-    </row>
-    <row r="90" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L89" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A90" s="17" t="s">
         <v>288</v>
       </c>
@@ -5527,13 +5824,16 @@
         <v>290</v>
       </c>
       <c r="J90" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K90" s="4">
         <v>92000</v>
       </c>
-    </row>
-    <row r="91" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L90" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>291</v>
       </c>
@@ -5562,13 +5862,16 @@
         <v>293</v>
       </c>
       <c r="J91" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K91" s="4">
         <v>151558</v>
       </c>
-    </row>
-    <row r="92" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L91" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>294</v>
       </c>
@@ -5597,13 +5900,16 @@
         <v>296</v>
       </c>
       <c r="J92" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K92" s="4">
         <v>92000</v>
       </c>
-    </row>
-    <row r="93" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L92" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>297</v>
       </c>
@@ -5632,13 +5938,16 @@
         <v>299</v>
       </c>
       <c r="J93" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K93" s="4">
         <v>151558</v>
       </c>
-    </row>
-    <row r="94" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L93" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>300</v>
       </c>
@@ -5667,13 +5976,16 @@
         <v>302</v>
       </c>
       <c r="J94" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K94" s="4">
         <v>92000</v>
       </c>
-    </row>
-    <row r="95" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L94" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>303</v>
       </c>
@@ -5702,13 +6014,16 @@
         <v>305</v>
       </c>
       <c r="J95" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K95" s="4">
         <v>151558</v>
       </c>
-    </row>
-    <row r="96" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L95" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>306</v>
       </c>
@@ -5737,13 +6052,16 @@
         <v>308</v>
       </c>
       <c r="J96" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K96" s="4">
         <v>92000</v>
       </c>
-    </row>
-    <row r="97" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L96" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>309</v>
       </c>
@@ -5772,13 +6090,16 @@
         <v>311</v>
       </c>
       <c r="J97" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K97" s="4">
         <v>151558</v>
       </c>
-    </row>
-    <row r="98" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L97" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>312</v>
       </c>
@@ -5807,13 +6128,16 @@
         <v>314</v>
       </c>
       <c r="J98" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K98" s="4">
         <v>151558</v>
       </c>
-    </row>
-    <row r="99" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L98" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>315</v>
       </c>
@@ -5842,13 +6166,16 @@
         <v>317</v>
       </c>
       <c r="J99" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K99" s="4">
         <v>151558</v>
       </c>
-    </row>
-    <row r="100" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L99" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>318</v>
       </c>
@@ -5877,13 +6204,16 @@
         <v>320</v>
       </c>
       <c r="J100" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K100" s="4">
         <v>151558</v>
       </c>
-    </row>
-    <row r="101" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L100" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>321</v>
       </c>
@@ -5912,13 +6242,16 @@
         <v>323</v>
       </c>
       <c r="J101" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K101" s="8">
         <v>116055</v>
       </c>
-    </row>
-    <row r="102" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L101" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>324</v>
       </c>
@@ -5947,13 +6280,16 @@
         <v>326</v>
       </c>
       <c r="J102" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K102" s="8">
         <v>116055</v>
       </c>
-    </row>
-    <row r="103" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L102" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>327</v>
       </c>
@@ -5982,13 +6318,16 @@
         <v>329</v>
       </c>
       <c r="J103" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K103" s="8" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="104" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L103" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>330</v>
       </c>
@@ -6017,13 +6356,16 @@
         <v>332</v>
       </c>
       <c r="J104" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K104" s="4">
         <v>151558</v>
       </c>
-    </row>
-    <row r="105" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="L104" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>333</v>
       </c>
@@ -6052,14 +6394,17 @@
         <v>335</v>
       </c>
       <c r="J105" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K105" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="106" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A106" s="30" t="s">
+      <c r="L105" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A106" s="29" t="s">
         <v>336</v>
       </c>
       <c r="B106" s="14" t="s">
@@ -6074,7 +6419,7 @@
       <c r="E106" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="F106" s="31" t="s">
+      <c r="F106" s="30" t="s">
         <v>339</v>
       </c>
       <c r="G106" s="13" t="s">
@@ -6087,14 +6432,17 @@
         <v>342</v>
       </c>
       <c r="J106" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K106" s="16">
         <v>0</v>
       </c>
-    </row>
-    <row r="107" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A107" s="32" t="s">
+      <c r="L106" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A107" s="31" t="s">
         <v>343</v>
       </c>
       <c r="B107" s="2" t="s">
@@ -6109,7 +6457,7 @@
       <c r="E107" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F107" s="33" t="s">
+      <c r="F107" s="32" t="s">
         <v>344</v>
       </c>
       <c r="G107" s="2" t="s">
@@ -6122,14 +6470,17 @@
         <v>346</v>
       </c>
       <c r="J107" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K107" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="108" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A108" s="34" t="s">
+      <c r="L107" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A108" s="33" t="s">
         <v>347</v>
       </c>
       <c r="B108" s="1" t="s">
@@ -6144,7 +6495,7 @@
       <c r="E108" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F108" s="35" t="s">
+      <c r="F108" s="34" t="s">
         <v>350</v>
       </c>
       <c r="G108" s="1" t="s">
@@ -6157,14 +6508,17 @@
         <v>351</v>
       </c>
       <c r="J108" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K108" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A109" s="36" t="s">
+      <c r="L108" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A109" s="35" t="s">
         <v>352</v>
       </c>
       <c r="B109" s="1" t="s">
@@ -6179,7 +6533,7 @@
       <c r="E109" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F109" s="35" t="s">
+      <c r="F109" s="34" t="s">
         <v>354</v>
       </c>
       <c r="G109" s="1" t="s">
@@ -6192,14 +6546,17 @@
         <v>355</v>
       </c>
       <c r="J109" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
       <c r="K109" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="110" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A110" s="36" t="s">
+      <c r="L109" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A110" s="35" t="s">
         <v>356</v>
       </c>
       <c r="B110" s="1" t="s">
@@ -6220,18 +6577,21 @@
       <c r="G110" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H110" s="36" t="s">
+      <c r="H110" s="35" t="s">
         <v>341</v>
       </c>
-      <c r="I110" s="37" t="s">
+      <c r="I110" s="36" t="s">
         <v>358</v>
       </c>
       <c r="J110" s="3">
-        <v>124587</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A111" s="36"/>
+        <v>1234</v>
+      </c>
+      <c r="L110" s="41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A111" s="35"/>
       <c r="B111" s="1" t="s">
         <v>359</v>
       </c>
@@ -6250,16 +6610,18 @@
       <c r="G111" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H111" s="36" t="s">
+      <c r="H111" s="35" t="s">
         <v>341</v>
       </c>
-      <c r="I111" s="37"/>
-      <c r="J111" s="3">
-        <v>124587</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A112" s="36" t="s">
+      <c r="I111" s="36" t="s">
+        <v>410</v>
+      </c>
+      <c r="J111" s="40">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A112" s="35" t="s">
         <v>360</v>
       </c>
       <c r="B112" s="1" t="s">
@@ -6280,18 +6642,18 @@
       <c r="G112" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H112" s="36" t="s">
+      <c r="H112" s="35" t="s">
         <v>341</v>
       </c>
-      <c r="I112" s="37" t="s">
+      <c r="I112" s="36" t="s">
         <v>362</v>
       </c>
       <c r="J112" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="113" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A113" s="36" t="s">
+      <c r="A113" s="35" t="s">
         <v>363</v>
       </c>
       <c r="B113" s="1" t="s">
@@ -6312,18 +6674,18 @@
       <c r="G113" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H113" s="36" t="s">
+      <c r="H113" s="35" t="s">
         <v>341</v>
       </c>
-      <c r="I113" s="37" t="s">
+      <c r="I113" s="36" t="s">
         <v>365</v>
       </c>
       <c r="J113" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="114" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A114" s="36" t="s">
+      <c r="A114" s="35" t="s">
         <v>366</v>
       </c>
       <c r="B114" s="1" t="s">
@@ -6344,18 +6706,18 @@
       <c r="G114" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H114" s="36" t="s">
+      <c r="H114" s="35" t="s">
         <v>341</v>
       </c>
-      <c r="I114" s="37" t="s">
+      <c r="I114" s="36" t="s">
         <v>368</v>
       </c>
       <c r="J114" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="115" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A115" s="36" t="s">
+      <c r="A115" s="35" t="s">
         <v>369</v>
       </c>
       <c r="B115" s="1" t="s">
@@ -6376,18 +6738,18 @@
       <c r="G115" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H115" s="36" t="s">
+      <c r="H115" s="35" t="s">
         <v>341</v>
       </c>
-      <c r="I115" s="37" t="s">
+      <c r="I115" s="36" t="s">
         <v>371</v>
       </c>
       <c r="J115" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="116" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A116" s="36" t="s">
+      <c r="A116" s="35" t="s">
         <v>372</v>
       </c>
       <c r="B116" s="1" t="s">
@@ -6408,18 +6770,18 @@
       <c r="G116" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H116" s="36" t="s">
+      <c r="H116" s="35" t="s">
         <v>341</v>
       </c>
-      <c r="I116" s="37" t="s">
+      <c r="I116" s="36" t="s">
         <v>374</v>
       </c>
-      <c r="J116" s="3">
-        <v>124587</v>
+      <c r="J116" s="40">
+        <v>1234</v>
       </c>
     </row>
     <row r="117" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A117" s="36" t="s">
+      <c r="A117" s="35" t="s">
         <v>375</v>
       </c>
       <c r="B117" s="1" t="s">
@@ -6440,18 +6802,18 @@
       <c r="G117" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H117" s="36" t="s">
+      <c r="H117" s="35" t="s">
         <v>341</v>
       </c>
-      <c r="I117" s="37" t="s">
+      <c r="I117" s="36" t="s">
         <v>377</v>
       </c>
       <c r="J117" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="118" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A118" s="36"/>
+      <c r="A118" s="35"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1" t="s">
         <v>12</v>
@@ -6468,16 +6830,18 @@
       <c r="G118" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H118" s="36" t="s">
+      <c r="H118" s="35" t="s">
         <v>341</v>
       </c>
-      <c r="I118" s="37"/>
+      <c r="I118" s="36" t="s">
+        <v>380</v>
+      </c>
       <c r="J118" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="119" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A119" s="36" t="s">
+      <c r="A119" s="35" t="s">
         <v>378</v>
       </c>
       <c r="B119" s="1" t="s">
@@ -6498,18 +6862,18 @@
       <c r="G119" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H119" s="36" t="s">
+      <c r="H119" s="35" t="s">
         <v>341</v>
       </c>
-      <c r="I119" s="37" t="s">
-        <v>380</v>
+      <c r="I119" s="36" t="s">
+        <v>409</v>
       </c>
       <c r="J119" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="120" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A120" s="36" t="s">
+      <c r="A120" s="35" t="s">
         <v>381</v>
       </c>
       <c r="B120" s="1" t="s">
@@ -6530,18 +6894,18 @@
       <c r="G120" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H120" s="36" t="s">
+      <c r="H120" s="35" t="s">
         <v>341</v>
       </c>
-      <c r="I120" s="37" t="s">
+      <c r="I120" s="36" t="s">
         <v>383</v>
       </c>
       <c r="J120" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="121" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A121" s="36" t="s">
+      <c r="A121" s="35" t="s">
         <v>381</v>
       </c>
       <c r="B121" s="1" t="s">
@@ -6562,18 +6926,18 @@
       <c r="G121" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H121" s="36" t="s">
+      <c r="H121" s="35" t="s">
         <v>341</v>
       </c>
-      <c r="I121" s="37" t="s">
+      <c r="I121" s="36" t="s">
         <v>385</v>
       </c>
-      <c r="J121" s="3">
-        <v>124587</v>
+      <c r="J121" s="40">
+        <v>1234</v>
       </c>
     </row>
     <row r="122" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A122" s="36" t="s">
+      <c r="A122" s="35" t="s">
         <v>386</v>
       </c>
       <c r="B122" s="1" t="s">
@@ -6594,18 +6958,18 @@
       <c r="G122" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H122" s="36" t="s">
+      <c r="H122" s="35" t="s">
         <v>341</v>
       </c>
-      <c r="I122" s="37" t="s">
+      <c r="I122" s="36" t="s">
         <v>388</v>
       </c>
       <c r="J122" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="123" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A123" s="36" t="s">
+      <c r="A123" s="35" t="s">
         <v>389</v>
       </c>
       <c r="B123" s="1" t="s">
@@ -6626,18 +6990,18 @@
       <c r="G123" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H123" s="36" t="s">
+      <c r="H123" s="35" t="s">
         <v>341</v>
       </c>
-      <c r="I123" s="37" t="s">
+      <c r="I123" s="36" t="s">
         <v>391</v>
       </c>
       <c r="J123" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="124" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A124" s="36" t="s">
+      <c r="A124" s="35" t="s">
         <v>392</v>
       </c>
       <c r="B124" s="1" t="s">
@@ -6658,18 +7022,18 @@
       <c r="G124" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H124" s="36" t="s">
+      <c r="H124" s="35" t="s">
         <v>341</v>
       </c>
-      <c r="I124" s="37" t="s">
+      <c r="I124" s="36" t="s">
         <v>394</v>
       </c>
       <c r="J124" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="125" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A125" s="36" t="s">
+      <c r="A125" s="35" t="s">
         <v>395</v>
       </c>
       <c r="B125" s="1" t="s">
@@ -6690,18 +7054,18 @@
       <c r="G125" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H125" s="36" t="s">
+      <c r="H125" s="35" t="s">
         <v>341</v>
       </c>
-      <c r="I125" s="37" t="s">
+      <c r="I125" s="36" t="s">
         <v>397</v>
       </c>
       <c r="J125" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="126" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A126" s="36" t="s">
+      <c r="A126" s="35" t="s">
         <v>398</v>
       </c>
       <c r="B126" s="1" t="s">
@@ -6722,18 +7086,18 @@
       <c r="G126" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H126" s="36" t="s">
+      <c r="H126" s="35" t="s">
         <v>341</v>
       </c>
-      <c r="I126" s="37" t="s">
+      <c r="I126" s="36" t="s">
         <v>400</v>
       </c>
-      <c r="J126" s="3">
-        <v>124587</v>
+      <c r="J126" s="40">
+        <v>1234</v>
       </c>
     </row>
     <row r="127" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A127" s="36" t="s">
+      <c r="A127" s="35" t="s">
         <v>401</v>
       </c>
       <c r="B127" s="1" t="s">
@@ -6754,18 +7118,18 @@
       <c r="G127" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H127" s="36" t="s">
+      <c r="H127" s="35" t="s">
         <v>341</v>
       </c>
-      <c r="I127" s="37" t="s">
+      <c r="I127" s="36" t="s">
         <v>403</v>
       </c>
       <c r="J127" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="128" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A128" s="36" t="s">
+      <c r="A128" s="35" t="s">
         <v>404</v>
       </c>
       <c r="B128" s="1" t="s">
@@ -6786,14 +7150,14 @@
       <c r="G128" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H128" s="36" t="s">
+      <c r="H128" s="35" t="s">
         <v>341</v>
       </c>
-      <c r="I128" s="37" t="s">
+      <c r="I128" s="36" t="s">
         <v>406</v>
       </c>
       <c r="J128" s="3">
-        <v>124587</v>
+        <v>1234</v>
       </c>
     </row>
   </sheetData>
